--- a/data/trans_bre/P8_1_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P8_1_R-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 13,03</t>
+          <t>0,17; 12,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,13; 18,95</t>
+          <t>4,94; 18,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,72; 16,35</t>
+          <t>1,97; 16,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 9,49</t>
+          <t>-1,68; 8,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 147,97</t>
+          <t>0,2; 130,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,23; 141,04</t>
+          <t>25,37; 137,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,04; 110,01</t>
+          <t>5,77; 104,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 78,23</t>
+          <t>-9,05; 72,48</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,54; 17,09</t>
+          <t>7,38; 16,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,04; 17,64</t>
+          <t>7,19; 17,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,17; 13,75</t>
+          <t>4,33; 13,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,01; 11,86</t>
+          <t>2,97; 11,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>52,54; 174,17</t>
+          <t>52,77; 173,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,49; 143,39</t>
+          <t>40,96; 144,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,48; 136,22</t>
+          <t>29,49; 136,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,9; 85,91</t>
+          <t>14,36; 88,63</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,77; 19,33</t>
+          <t>8,82; 19,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,44; 14,81</t>
+          <t>2,59; 14,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 12,44</t>
+          <t>0,21; 12,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 10,78</t>
+          <t>1,82; 11,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>85,53; 357,35</t>
+          <t>86,51; 365,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,6; 125,67</t>
+          <t>12,28; 122,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,46; 111,01</t>
+          <t>1,23; 116,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,29; 99,59</t>
+          <t>11,99; 107,79</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,15; 16,05</t>
+          <t>6,77; 16,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,07; 21,86</t>
+          <t>9,75; 22,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,22; 18,25</t>
+          <t>6,2; 17,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,57; 6,15</t>
+          <t>-9,34; 6,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>51,56; 226,76</t>
+          <t>56,35; 256,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,1; 188,78</t>
+          <t>54,92; 189,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,3; 147,85</t>
+          <t>35,18; 155,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,98; 39,2</t>
+          <t>-42,39; 39,46</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,58; 15,65</t>
+          <t>3,28; 16,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,43; 19,67</t>
+          <t>4,24; 20,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,32; 16,99</t>
+          <t>2,49; 16,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 13,63</t>
+          <t>-1,78; 13,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>36,61; 291,84</t>
+          <t>32,26; 338,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,25; 158,77</t>
+          <t>19,67; 157,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,65; 177,1</t>
+          <t>11,56; 171,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-16,57; 133,18</t>
+          <t>-11,29; 137,3</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,41; 20,86</t>
+          <t>7,59; 20,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,25; 15,94</t>
+          <t>2,09; 16,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,7; 17,88</t>
+          <t>3,33; 18,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,08; 10,85</t>
+          <t>2,0; 11,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>55,35; 276,77</t>
+          <t>55,12; 247,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,21; 103,03</t>
+          <t>8,76; 112,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,78; 105,81</t>
+          <t>12,98; 109,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15,86; 133,63</t>
+          <t>13,58; 130,87</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,6; 12,94</t>
+          <t>4,79; 12,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,02; 15,47</t>
+          <t>7,53; 15,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,74; 12,33</t>
+          <t>3,88; 12,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 8,72</t>
+          <t>-8,52; 8,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32,52; 129,59</t>
+          <t>34,42; 124,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,09; 149,0</t>
+          <t>51,09; 152,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,25; 110,48</t>
+          <t>25,41; 111,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-47,35; 56,71</t>
+          <t>-44,79; 59,22</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,45; 11,7</t>
+          <t>4,42; 11,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,06; 11,02</t>
+          <t>2,98; 10,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,7; 11,87</t>
+          <t>4,27; 11,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-47,12; 12,44</t>
+          <t>-46,67; 12,58</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,14; 105,73</t>
+          <t>27,56; 102,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,02; 91,08</t>
+          <t>17,13; 86,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,91; 123,04</t>
+          <t>31,76; 118,79</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-66,95; 100,6</t>
+          <t>-65,74; 101,09</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,48; 12,04</t>
+          <t>8,41; 12,1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,73; 12,67</t>
+          <t>8,66; 12,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,93; 10,62</t>
+          <t>7,08; 10,69</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-21,26; 6,37</t>
+          <t>-17,8; 6,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>71,36; 115,43</t>
+          <t>70,26; 115,61</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>56,04; 92,82</t>
+          <t>55,61; 92,09</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>47,66; 81,36</t>
+          <t>48,08; 82,4</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-52,8; 43,65</t>
+          <t>-46,88; 46,51</t>
         </is>
       </c>
     </row>
